--- a/tame_output/ON/bt/strategyON_20240312.xlsx
+++ b/tame_output/ON/bt/strategyON_20240312.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,17 +949,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>99.9%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>463.5%</t>
+          <t>465.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-80.2%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-203.5%</t>
+          <t>-207.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-79.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-121.4%</t>
+          <t>-185.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-80.7%</t>
+          <t>-99.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>83.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-02-12</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-56.6%</t>
         </is>
       </c>
     </row>
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-4.305536646396395</v>
+        <v>-4.747943804175743</v>
       </c>
       <c r="E1870" t="n">
-        <v>1.394591071950288</v>
+        <v>1.217628208838548</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.2382384104825251</v>
+        <v>-0.4277401577246012</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.974219108533078</v>
+        <v>2.860518060187832</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-4.303419487672103</v>
+        <v>-4.745826645451451</v>
       </c>
       <c r="E1871" t="n">
-        <v>1.391411630905601</v>
+        <v>1.214448767793862</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.2382384104825251</v>
+        <v>-0.4277401577246012</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.970192803998675</v>
+        <v>2.856491755653429</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-4.302942141093613</v>
+        <v>-4.745349298872961</v>
       </c>
       <c r="E1872" t="n">
-        <v>1.391500468215413</v>
+        <v>1.214537605103674</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.2382384104825251</v>
+        <v>-0.4277401577246012</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.970090702677091</v>
+        <v>2.856389654331845</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-4.301917354786755</v>
+        <v>-4.744324512566103</v>
       </c>
       <c r="E1873" t="n">
-        <v>1.394481898709587</v>
+        <v>1.217519035597847</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.2372136241756675</v>
+        <v>-0.4267153714177436</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.973277090432636</v>
+        <v>2.85957604208739</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-4.320658735045674</v>
+        <v>-4.763065892825022</v>
       </c>
       <c r="E1874" t="n">
-        <v>1.392335649904069</v>
+        <v>1.21537278679233</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.2372136241756675</v>
+        <v>-0.4267153714177436</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.978627393730686</v>
+        <v>2.86492634538544</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-4.333628077830772</v>
+        <v>-4.77603523561012</v>
       </c>
       <c r="E1875" t="n">
-        <v>1.395063932747207</v>
+        <v>1.218101069635468</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.2501829669607661</v>
+        <v>-0.4396847142028421</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.978761808016804</v>
+        <v>2.865060759671559</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-4.327151931037212</v>
+        <v>-4.76955908881656</v>
       </c>
       <c r="E1876" t="n">
-        <v>1.4006961420864</v>
+        <v>1.223733278974661</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.2437068201672065</v>
+        <v>-0.4332085674092825</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.985689246714709</v>
+        <v>2.871988198369463</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-4.323461006080801</v>
+        <v>-4.765868163860149</v>
       </c>
       <c r="E1877" t="n">
-        <v>1.402172512068965</v>
+        <v>1.225209648957226</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.2437068201672065</v>
+        <v>-0.4332085674092825</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.985689246714709</v>
+        <v>2.871988198369463</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-4.316245653208985</v>
+        <v>-4.758652810988333</v>
       </c>
       <c r="E1878" t="n">
-        <v>1.410571850336334</v>
+        <v>1.233608987224594</v>
       </c>
       <c r="F1878" t="n">
-        <v>-0.1739285848768247</v>
+        <v>-0.3634303321189007</v>
       </c>
       <c r="G1878" t="n">
-        <v>3.03306938500758</v>
+        <v>2.919368336662335</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-4.265217807127159</v>
+        <v>-4.707624964906507</v>
       </c>
       <c r="E1879" t="n">
-        <v>1.4354655432535</v>
+        <v>1.258502680141761</v>
       </c>
       <c r="F1879" t="n">
-        <v>-0.0987192465697237</v>
+        <v>-0.2882209938117997</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.082677542476277</v>
+        <v>2.968976494131031</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-4.191747975459711</v>
+        <v>-4.634155133239059</v>
       </c>
       <c r="E1880" t="n">
-        <v>1.4802251774139</v>
+        <v>1.303262314302161</v>
       </c>
       <c r="F1880" t="n">
-        <v>-0.02524941490227528</v>
+        <v>-0.2147511621443513</v>
       </c>
       <c r="G1880" t="n">
-        <v>3.142131142970167</v>
+        <v>3.028430094624921</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-4.111375619995781</v>
+        <v>-4.553782777775129</v>
       </c>
       <c r="E1881" t="n">
-        <v>1.526929340346989</v>
+        <v>1.34996647723525</v>
       </c>
       <c r="F1881" t="n">
-        <v>0.05512294056165434</v>
+        <v>-0.1343788066804217</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.204909776996042</v>
+        <v>3.091208728650796</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-4.07844375018293</v>
+        <v>-4.520850907962278</v>
       </c>
       <c r="E1882" t="n">
-        <v>1.532882923370533</v>
+        <v>1.355920060258794</v>
       </c>
       <c r="F1882" t="n">
-        <v>0.05512294056165434</v>
+        <v>-0.1343788066804217</v>
       </c>
       <c r="G1882" t="n">
-        <v>3.197690612094445</v>
+        <v>3.0839895637492</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-4.098608391732477</v>
+        <v>-4.541015549511825</v>
       </c>
       <c r="E1883" t="n">
-        <v>1.518144875976738</v>
+        <v>1.341182012864999</v>
       </c>
       <c r="F1883" t="n">
-        <v>0.03495829901210701</v>
+        <v>-0.154543448229969</v>
       </c>
       <c r="G1883" t="n">
-        <v>3.178919636390741</v>
+        <v>3.065218588045496</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-4.039941461710944</v>
+        <v>-4.482348619490292</v>
       </c>
       <c r="E1884" t="n">
-        <v>1.542727437823908</v>
+        <v>1.365764574712169</v>
       </c>
       <c r="F1884" t="n">
-        <v>0.1199177674422447</v>
+        <v>-0.06958397979983133</v>
       </c>
       <c r="G1884" t="n">
-        <v>3.23101110728738</v>
+        <v>3.117310058942135</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-3.976872229404604</v>
+        <v>-4.419279387183952</v>
       </c>
       <c r="E1885" t="n">
-        <v>1.570648859375559</v>
+        <v>1.39368599626382</v>
       </c>
       <c r="F1885" t="n">
-        <v>0.09140420476001021</v>
+        <v>-0.09809754248206581</v>
       </c>
       <c r="G1885" t="n">
-        <v>3.216596698307154</v>
+        <v>3.102895649961908</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-3.924856715435792</v>
+        <v>-4.36726387321514</v>
       </c>
       <c r="E1886" t="n">
-        <v>1.595445400649484</v>
+        <v>1.418482537537745</v>
       </c>
       <c r="F1886" t="n">
-        <v>0.09140420476001021</v>
+        <v>-0.09809754248206581</v>
       </c>
       <c r="G1886" t="n">
-        <v>3.220587033993555</v>
+        <v>3.106885985648309</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-3.749287046514888</v>
+        <v>-4.191694204294236</v>
       </c>
       <c r="E1887" t="n">
-        <v>1.664198041319104</v>
+        <v>1.487235178207365</v>
       </c>
       <c r="F1887" t="n">
-        <v>0.09140420476001021</v>
+        <v>-0.09809754248206581</v>
       </c>
       <c r="G1887" t="n">
-        <v>3.219111807094813</v>
+        <v>3.105410758749568</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-3.55201764078689</v>
+        <v>-3.994424798566238</v>
       </c>
       <c r="E1888" t="n">
-        <v>1.758159213775176</v>
+        <v>1.581196350663437</v>
       </c>
       <c r="F1888" t="n">
-        <v>0.2886736104880083</v>
+        <v>0.0991718632459323</v>
       </c>
       <c r="G1888" t="n">
-        <v>3.352526860696484</v>
+        <v>3.238825812351239</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-3.352865533549791</v>
+        <v>-3.795272691329139</v>
       </c>
       <c r="E1889" t="n">
-        <v>1.824768923023333</v>
+        <v>1.647806059911593</v>
       </c>
       <c r="F1889" t="n">
-        <v>0.4539961364378217</v>
+        <v>0.2644943891957456</v>
       </c>
       <c r="G1889" t="n">
-        <v>3.438669242619689</v>
+        <v>3.324968194274444</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-3.12702038083038</v>
+        <v>-3.569427538609728</v>
       </c>
       <c r="E1890" t="n">
-        <v>1.924686057147305</v>
+        <v>1.747723194035566</v>
       </c>
       <c r="F1890" t="n">
-        <v>0.4959228120249853</v>
+        <v>0.3064210647829093</v>
       </c>
       <c r="G1890" t="n">
-        <v>3.473404321008196</v>
+        <v>3.359703272662951</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-2.840745568507685</v>
+        <v>-3.283152726287033</v>
       </c>
       <c r="E1891" t="n">
-        <v>2.040335126632442</v>
+        <v>1.863372263520703</v>
       </c>
       <c r="F1891" t="n">
-        <v>0.4959228120249853</v>
+        <v>0.3064210647829093</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.474543465564255</v>
+        <v>3.360842417219009</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-2.613949741434352</v>
+        <v>-3.0563568992137</v>
       </c>
       <c r="E1892" t="n">
-        <v>2.133687231623883</v>
+        <v>1.956724368512144</v>
       </c>
       <c r="F1892" t="n">
-        <v>0.5640367566465299</v>
+        <v>0.3745350094044538</v>
       </c>
       <c r="G1892" t="n">
-        <v>3.518045606499289</v>
+        <v>3.404344558154044</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-2.330041010505603</v>
+        <v>-2.772448168284951</v>
       </c>
       <c r="E1893" t="n">
-        <v>2.252984428234019</v>
+        <v>2.07602156512228</v>
       </c>
       <c r="F1893" t="n">
-        <v>0.5640367566465299</v>
+        <v>0.3745350094044538</v>
       </c>
       <c r="G1893" t="n">
-        <v>3.523779310737926</v>
+        <v>3.41007826239268</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-2.083053760312651</v>
+        <v>-2.525460918091999</v>
       </c>
       <c r="E1894" t="n">
-        <v>2.342042065917335</v>
+        <v>2.165079202805596</v>
       </c>
       <c r="F1894" t="n">
-        <v>0.8110240068394819</v>
+        <v>0.6215222595974059</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.662234398459832</v>
+        <v>3.548533350114586</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-1.819216893108582</v>
+        <v>-2.26162405088793</v>
       </c>
       <c r="E1895" t="n">
-        <v>2.437693331486055</v>
+        <v>2.260730468374316</v>
       </c>
       <c r="F1895" t="n">
-        <v>0.8110240068394819</v>
+        <v>0.6215222595974059</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.652350917146924</v>
+        <v>3.538649868801679</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-1.551975092240185</v>
+        <v>-1.994382250019533</v>
       </c>
       <c r="E1896" t="n">
-        <v>2.54275549133404</v>
+        <v>2.365792628222301</v>
       </c>
       <c r="F1896" t="n">
-        <v>0.8110240068394819</v>
+        <v>0.6215222595974059</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.650516356647551</v>
+        <v>3.536815308302305</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-1.2761659288397</v>
+        <v>-1.718573086619049</v>
       </c>
       <c r="E1897" t="n">
-        <v>2.652778841720773</v>
+        <v>2.475815978609034</v>
       </c>
       <c r="F1897" t="n">
-        <v>0.9000433151182154</v>
+        <v>0.7105415678761394</v>
       </c>
       <c r="G1897" t="n">
-        <v>3.70362762664133</v>
+        <v>3.589926578296084</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-1.007098341072721</v>
+        <v>-1.449505498852069</v>
       </c>
       <c r="E1898" t="n">
-        <v>2.761074382973058</v>
+        <v>2.584111519861319</v>
       </c>
       <c r="F1898" t="n">
-        <v>1.169110902885195</v>
+        <v>0.9796091556431188</v>
       </c>
       <c r="G1898" t="n">
-        <v>3.865736685447011</v>
+        <v>3.752035637101765</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-0.7430384027499251</v>
+        <v>-1.185445560529273</v>
       </c>
       <c r="E1899" t="n">
-        <v>2.853438042140425</v>
+        <v>2.676475179028685</v>
       </c>
       <c r="F1899" t="n">
-        <v>1.433170841207991</v>
+        <v>1.243669093965915</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.010912332278937</v>
+        <v>3.897211283933691</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.47633013459772</v>
+        <v>3.485342674753666</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-0.4191677178518887</v>
+        <v>-0.457850911787293</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.980199282439338</v>
+        <v>2.964726004865176</v>
       </c>
       <c r="F1900" t="n">
-        <v>1.433170841207991</v>
+        <v>1.243669093965915</v>
       </c>
       <c r="G1900" t="n">
-        <v>4.008125298618636</v>
+        <v>3.89442425027339</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240312.xlsx
+++ b/tame_output/ON/bt/strategyON_20240312.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-43.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1002,22 +1002,22 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>465.5%</t>
+          <t>461.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-207.4%</t>
+          <t>-247.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-95.8%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923092</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.78468094578195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567246</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487775</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.485342674753666</v>
+        <v>3.485342674753668</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-0.457850911787293</v>
+        <v>-0.8592270782976844</v>
       </c>
       <c r="E1900" t="n">
-        <v>2.964726004865176</v>
+        <v>2.80417553826102</v>
       </c>
       <c r="F1900" t="n">
         <v>1.243669093965915</v>

--- a/tame_output/ON/bt/strategyON_20240312.xlsx
+++ b/tame_output/ON/bt/strategyON_20240312.xlsx
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923092</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>

--- a/tame_output/ON/bt/strategyON_20240312.xlsx
+++ b/tame_output/ON/bt/strategyON_20240312.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-219.2%</t>
+          <t>-219.5%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-84.4%</t>
+          <t>-84.6%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-53.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>103.8%</t>
+          <t>103.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>99.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-28.8%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-0.5760633443162914</v>
+        <v>-0.5794331399559689</v>
       </c>
       <c r="E1901" t="n">
-        <v>2.917784655741419</v>
+        <v>2.916436737485548</v>
       </c>
       <c r="F1901" t="n">
-        <v>1.709393684244566</v>
+        <v>1.706023888604888</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.174202628328421</v>
+        <v>4.172180750944616</v>
       </c>
     </row>
   </sheetData>
